--- a/output/2026-09-08_19_Croazia_Sisacko-moslavacka_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-08_19_Croazia_Sisacko-moslavacka_Depolverazione_Trattamento_aria.xlsx
@@ -474,7 +474,6 @@
           <t>VEK SISTEMI SISAK d.o.o.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Hrastelnica, Sisak (Contea Sisačko-moslavačka)</t>
@@ -502,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -544,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
